--- a/results/mfdwc_experiment_results.xlsx
+++ b/results/mfdwc_experiment_results.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\UDA-mfdwc-wavelet_features\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFC82F01-7686-493A-A82D-05E905ACDE46}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{174A5B38-0336-42EB-91B6-C211E8282C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" activeTab="1" xr2:uid="{207E8739-F5E8-4D4F-9227-D53A58B985A3}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10890" activeTab="1" xr2:uid="{207E8739-F5E8-4D4F-9227-D53A58B985A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -172,7 +172,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="11">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -180,25 +180,18 @@
     <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
     <xf numFmtId="10" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="10" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="10" fontId="3" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -544,26 +537,26 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:4" ht="24.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="3"/>
+      <c r="D1" s="7"/>
     </row>
     <row r="2" spans="1:4" ht="41.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>10</v>
       </c>
     </row>
@@ -672,48 +665,48 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="23.5" x14ac:dyDescent="0.35">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3" t="s">
+      <c r="B1" s="7"/>
+      <c r="C1" s="7" t="s">
         <v>11</v>
       </c>
-      <c r="D1" s="3"/>
-      <c r="E1" s="3"/>
+      <c r="D1" s="7"/>
+      <c r="E1" s="7"/>
     </row>
     <row r="2" spans="1:5" ht="34.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="3" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>14</v>
       </c>
-      <c r="D2" s="5" t="s">
+      <c r="D2" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="E2" s="5" t="s">
+      <c r="E2" s="4" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="3" spans="1:5" s="6" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="7" t="s">
-        <v>2</v>
-      </c>
-      <c r="C3" s="10">
+    <row r="3" spans="1:5" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="C3" s="2">
         <v>0.81210000000000004</v>
       </c>
-      <c r="D3" s="9">
+      <c r="D3" s="6">
         <v>0.76670000000000005</v>
       </c>
-      <c r="E3" s="10">
-        <v>0.79090000000000005</v>
+      <c r="E3" s="2">
+        <v>0.78480000000000005</v>
       </c>
     </row>
     <row r="4" spans="1:5" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -724,13 +717,13 @@
         <v>3</v>
       </c>
       <c r="C4" s="2">
-        <v>0.60899999999999999</v>
+        <v>0.62919999999999998</v>
       </c>
       <c r="D4" s="2">
         <v>0.68689999999999996</v>
       </c>
       <c r="E4" s="2">
-        <v>0.63529999999999998</v>
+        <v>0.63829999999999998</v>
       </c>
     </row>
     <row r="5" spans="1:5" ht="28" customHeight="1" x14ac:dyDescent="0.35">
@@ -741,13 +734,13 @@
         <v>4</v>
       </c>
       <c r="C5" s="2">
-        <v>0.69899999999999995</v>
+        <v>0.71730000000000005</v>
       </c>
       <c r="D5" s="2">
         <v>0.74160000000000004</v>
       </c>
       <c r="E5" s="2">
-        <v>0.73250000000000004</v>
+        <v>0.74770000000000003</v>
       </c>
     </row>
     <row r="6" spans="1:5" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -758,7 +751,7 @@
         <v>5</v>
       </c>
       <c r="C6" s="2">
-        <v>0.41199999999999998</v>
+        <v>0.48180000000000001</v>
       </c>
       <c r="D6" s="2">
         <v>0.63639999999999997</v>
@@ -775,13 +768,13 @@
         <v>6</v>
       </c>
       <c r="C7" s="2">
-        <v>0.40799999999999997</v>
+        <v>0.39389999999999997</v>
       </c>
       <c r="D7" s="2">
         <v>0.59089999999999998</v>
       </c>
       <c r="E7" s="2">
-        <v>0.503</v>
+        <v>0.5091</v>
       </c>
     </row>
     <row r="8" spans="1:5" ht="29.5" customHeight="1" x14ac:dyDescent="0.35">
@@ -792,23 +785,23 @@
         <v>7</v>
       </c>
       <c r="C8" s="2">
-        <v>0.46500000000000002</v>
+        <v>0.47270000000000001</v>
       </c>
       <c r="D8" s="2">
         <v>0.61819999999999997</v>
       </c>
       <c r="E8" s="2">
-        <v>0.58789999999999998</v>
+        <v>0.57579999999999998</v>
       </c>
     </row>
     <row r="9" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="D9" s="8"/>
+      <c r="D9" s="5"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="D10" s="8"/>
+      <c r="D10" s="5"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="D11" s="8"/>
+      <c r="D11" s="5"/>
     </row>
   </sheetData>
   <mergeCells count="2">

--- a/results/mfdwc_experiment_results.xlsx
+++ b/results/mfdwc_experiment_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\UDA-mfdwc-wavelet_features\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{174A5B38-0336-42EB-91B6-C211E8282C48}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFFC4D3D-8EC6-47EF-B95F-99B4FE792538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10890" activeTab="1" xr2:uid="{207E8739-F5E8-4D4F-9227-D53A58B985A3}"/>
+    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10890" xr2:uid="{207E8739-F5E8-4D4F-9227-D53A58B985A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -568,10 +568,10 @@
         <v>2</v>
       </c>
       <c r="C3" s="2">
-        <v>0.63629999999999998</v>
+        <v>0.56969999999999998</v>
       </c>
       <c r="D3" s="2">
-        <v>0.62329999999999997</v>
+        <v>0.58789999999999998</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -613,7 +613,7 @@
         <v>0.30299999999999999</v>
       </c>
       <c r="D6" s="2">
-        <v>0.34839999999999999</v>
+        <v>0.34849999999999998</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -627,7 +627,7 @@
         <v>0.33939999999999998</v>
       </c>
       <c r="D7" s="2">
-        <v>0.36230000000000001</v>
+        <v>0.33029999999999998</v>
       </c>
     </row>
     <row r="8" spans="1:4" ht="30" customHeight="1" x14ac:dyDescent="0.35">
@@ -641,7 +641,7 @@
         <v>0.31819999999999998</v>
       </c>
       <c r="D8" s="2">
-        <v>0.33029999999999998</v>
+        <v>0.3276</v>
       </c>
     </row>
   </sheetData>

--- a/results/mfdwc_experiment_results.xlsx
+++ b/results/mfdwc_experiment_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\UDA-mfdwc-wavelet_features\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BFFC4D3D-8EC6-47EF-B95F-99B4FE792538}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4064EC7-3331-40DA-B4FA-BBB4D6B44862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="9510" yWindow="0" windowWidth="9780" windowHeight="10890" xr2:uid="{207E8739-F5E8-4D4F-9227-D53A58B985A3}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{207E8739-F5E8-4D4F-9227-D53A58B985A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -641,7 +641,7 @@
         <v>0.31819999999999998</v>
       </c>
       <c r="D8" s="2">
-        <v>0.3276</v>
+        <v>0.35749999999999998</v>
       </c>
     </row>
   </sheetData>

--- a/results/mfdwc_experiment_results.xlsx
+++ b/results/mfdwc_experiment_results.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\GitHub\UDA-mfdwc-wavelet_features\results\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E4064EC7-3331-40DA-B4FA-BBB4D6B44862}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CED112A5-8CBE-4944-BA62-9ACBB84A15BD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="11020" xr2:uid="{207E8739-F5E8-4D4F-9227-D53A58B985A3}"/>
+    <workbookView xWindow="7170" yWindow="2560" windowWidth="14400" windowHeight="7810" xr2:uid="{207E8739-F5E8-4D4F-9227-D53A58B985A3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -641,7 +641,7 @@
         <v>0.31819999999999998</v>
       </c>
       <c r="D8" s="2">
-        <v>0.35749999999999998</v>
+        <v>0.35759999999999997</v>
       </c>
     </row>
   </sheetData>
